--- a/experiment/HAT_bestx4/Test/results-Manga109/Manga109.xlsx
+++ b/experiment/HAT_bestx4/Test/results-Manga109/Manga109.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.44</v>
+        <v>28.49</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8189</v>
+        <v>0.8206</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.01</v>
+        <v>31.02</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8129</v>
+        <v>0.8134</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.24</v>
+        <v>28.27</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8451</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35.89</v>
+        <v>35.91</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9473</v>
+        <v>0.9476</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39.81</v>
+        <v>39.83</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9792</v>
+        <v>0.9795</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.08</v>
+        <v>30.12</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9147</v>
+        <v>0.9154</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33.13</v>
+        <v>33.24</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9565</v>
+        <v>0.9572000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.08</v>
+        <v>27.12</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8928</v>
+        <v>0.8935</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30.75</v>
+        <v>30.73</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9276</v>
+        <v>0.9277</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8953</v>
+        <v>0.8962</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29.65</v>
+        <v>29.83</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9503</v>
+        <v>0.9509</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28.05</v>
+        <v>28.07</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8632</v>
+        <v>0.8642</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33.44</v>
+        <v>33.67</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9616</v>
+        <v>0.9625</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32.03</v>
+        <v>32.09</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9025</v>
+        <v>0.9029</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.61</v>
+        <v>28.67</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9159</v>
+        <v>0.9169</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>27.64</v>
+        <v>27.66</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9075</v>
+        <v>0.9083</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30.98</v>
+        <v>30.99</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9562</v>
+        <v>0.956</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>34.54</v>
+        <v>34.56</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9767</v>
+        <v>0.9769</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30.75</v>
+        <v>30.82</v>
       </c>
       <c r="C20" t="n">
-        <v>0.901</v>
+        <v>0.9018</v>
       </c>
     </row>
     <row r="21">
@@ -702,7 +702,7 @@
         <v>32.87</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9757</v>
+        <v>0.9759</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32.02</v>
+        <v>32.07</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9231</v>
+        <v>0.9237</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32.18</v>
+        <v>32.26</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9356</v>
+        <v>0.9364</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30.18</v>
+        <v>30.24</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9121</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>37.09</v>
+        <v>37.3</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9715</v>
+        <v>0.9718</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29.08</v>
+        <v>29.15</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9565</v>
+        <v>0.9569</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>31.09</v>
+        <v>31.16</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9395</v>
+        <v>0.9402</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>38.3</v>
+        <v>38.34</v>
       </c>
       <c r="C28" t="n">
-        <v>0.978</v>
+        <v>0.9782</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.51</v>
+        <v>31.49</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9317</v>
+        <v>0.9315</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>33.19</v>
+        <v>33.33</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9587</v>
+        <v>0.9591</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31.28</v>
+        <v>31.39</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9414</v>
+        <v>0.9423</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26.84</v>
+        <v>26.87</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9385</v>
+        <v>0.9395</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="C33" t="n">
-        <v>0.929</v>
+        <v>0.9295</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32.5</v>
+        <v>32.55</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8925</v>
+        <v>0.8932</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>28.59</v>
+        <v>28.62</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7436</v>
+        <v>0.7444</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26.41</v>
+        <v>26.44</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8698</v>
+        <v>0.8706</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>31.47</v>
+        <v>31.54</v>
       </c>
       <c r="C37" t="n">
-        <v>0.911</v>
+        <v>0.9115</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>27.66</v>
+        <v>27.74</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.8648</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>35.18</v>
+        <v>35.27</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9707</v>
+        <v>0.9711</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>34.89</v>
+        <v>34.96</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9625</v>
       </c>
     </row>
     <row r="41">
@@ -962,7 +962,7 @@
         <v>28.17</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8978</v>
+        <v>0.8983</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>30.92</v>
+        <v>30.94</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8676</v>
+        <v>0.8682</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>32.73</v>
+        <v>32.76</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9154</v>
+        <v>0.9157999999999999</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>20.79</v>
+        <v>20.8</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7413</v>
+        <v>0.7431</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>35.04</v>
+        <v>35.14</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9766</v>
+        <v>0.9769</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25.1</v>
+        <v>25.11</v>
       </c>
       <c r="C46" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.9191</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>27.52</v>
+        <v>27.57</v>
       </c>
       <c r="C47" t="n">
-        <v>0.8967000000000001</v>
+        <v>0.8978</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>34.6</v>
+        <v>34.68</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9519</v>
+        <v>0.9525</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26.75</v>
+        <v>26.83</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8653</v>
+        <v>0.8671</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28.61</v>
+        <v>28.64</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9155</v>
+        <v>0.9161</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26.62</v>
+        <v>26.63</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7602</v>
+        <v>0.7607</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>30.24</v>
+        <v>30.35</v>
       </c>
       <c r="C52" t="n">
-        <v>0.946</v>
+        <v>0.9468</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>33.16</v>
+        <v>33.26</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9448</v>
+        <v>0.9457</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>36.33</v>
+        <v>36.36</v>
       </c>
       <c r="C54" t="n">
-        <v>0.9039</v>
+        <v>0.9041</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>35.63</v>
+        <v>35.73</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9626</v>
+        <v>0.9634</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>22.59</v>
+        <v>22.62</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7222</v>
+        <v>0.724</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>32.99</v>
+        <v>33.01</v>
       </c>
       <c r="C57" t="n">
-        <v>0.966</v>
+        <v>0.9661</v>
       </c>
     </row>
     <row r="58">
@@ -1183,7 +1183,7 @@
         <v>31.22</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9472</v>
+        <v>0.9474</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>31.77</v>
+        <v>31.89</v>
       </c>
       <c r="C59" t="n">
-        <v>0.9429</v>
+        <v>0.9438</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>23.72</v>
+        <v>23.75</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7635</v>
+        <v>0.7652</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>33.52</v>
+        <v>33.57</v>
       </c>
       <c r="C61" t="n">
-        <v>0.9704</v>
+        <v>0.9707</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.79</v>
+        <v>31.95</v>
       </c>
       <c r="C62" t="n">
-        <v>0.9466</v>
+        <v>0.9475</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>30.77</v>
+        <v>30.82</v>
       </c>
       <c r="C63" t="n">
-        <v>0.9488</v>
+        <v>0.9494</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>35.11</v>
+        <v>35.16</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9678</v>
+        <v>0.968</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>33.94</v>
+        <v>34.03</v>
       </c>
       <c r="C65" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.9273</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.18</v>
+        <v>25.17</v>
       </c>
       <c r="C66" t="n">
-        <v>0.9303</v>
+        <v>0.9301</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>32.11</v>
+        <v>32.25</v>
       </c>
       <c r="C67" t="n">
-        <v>0.9395</v>
+        <v>0.9406</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>32.97</v>
+        <v>33.05</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9312</v>
+        <v>0.9319</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>31.52</v>
+        <v>31.59</v>
       </c>
       <c r="C69" t="n">
-        <v>0.9394</v>
+        <v>0.9402</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>28.25</v>
+        <v>28.33</v>
       </c>
       <c r="C70" t="n">
-        <v>0.9219000000000001</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="71">
@@ -1352,7 +1352,7 @@
         <v>30.96</v>
       </c>
       <c r="C71" t="n">
-        <v>0.9376</v>
+        <v>0.9379999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -1365,7 +1365,7 @@
         <v>27.92</v>
       </c>
       <c r="C72" t="n">
-        <v>0.7122000000000001</v>
+        <v>0.7128</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>34.77</v>
+        <v>34.81</v>
       </c>
       <c r="C73" t="n">
-        <v>0.9576</v>
+        <v>0.958</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>33.78</v>
+        <v>33.84</v>
       </c>
       <c r="C74" t="n">
-        <v>0.9506</v>
+        <v>0.9513</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>28</v>
+        <v>28.06</v>
       </c>
       <c r="C75" t="n">
-        <v>0.888</v>
+        <v>0.8892</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>29.63</v>
+        <v>29.68</v>
       </c>
       <c r="C76" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.9016999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>30.23</v>
+        <v>30.31</v>
       </c>
       <c r="C77" t="n">
-        <v>0.9308</v>
+        <v>0.9312</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>30.13</v>
+        <v>30.18</v>
       </c>
       <c r="C78" t="n">
-        <v>0.8792</v>
+        <v>0.8803</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>27.96</v>
+        <v>28.01</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8087</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>30.94</v>
+        <v>30.97</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9329</v>
+        <v>0.9335</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>30.82</v>
+        <v>30.86</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9388</v>
+        <v>0.9393</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>29.77</v>
+        <v>29.81</v>
       </c>
       <c r="C82" t="n">
-        <v>0.8718</v>
+        <v>0.8725000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>31.84</v>
+        <v>31.88</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9033</v>
+        <v>0.9038</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>31.42</v>
+        <v>31.58</v>
       </c>
       <c r="C84" t="n">
-        <v>0.9594</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>27.52</v>
+        <v>27.58</v>
       </c>
       <c r="C85" t="n">
-        <v>0.9439</v>
+        <v>0.9449</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>32.24</v>
+        <v>32.28</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9314</v>
+        <v>0.9318</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>28.45</v>
+        <v>28.48</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8742</v>
+        <v>0.8746</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>35.46</v>
+        <v>35.68</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9519</v>
+        <v>0.953</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>33.85</v>
+        <v>33.87</v>
       </c>
       <c r="C89" t="n">
-        <v>0.9625</v>
+        <v>0.9627</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>30.27</v>
+        <v>30.3</v>
       </c>
       <c r="C90" t="n">
-        <v>0.9227</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>25.12</v>
+        <v>25.21</v>
       </c>
       <c r="C91" t="n">
-        <v>0.8591</v>
+        <v>0.8606</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>28.53</v>
+        <v>28.58</v>
       </c>
       <c r="C92" t="n">
-        <v>0.909</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>27.41</v>
+        <v>27.49</v>
       </c>
       <c r="C93" t="n">
-        <v>0.9486</v>
+        <v>0.9493</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>20.94</v>
+        <v>20.97</v>
       </c>
       <c r="C94" t="n">
-        <v>0.7341</v>
+        <v>0.7363</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>34.17</v>
+        <v>34.27</v>
       </c>
       <c r="C95" t="n">
-        <v>0.9554</v>
+        <v>0.9553</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>26.52</v>
+        <v>26.61</v>
       </c>
       <c r="C96" t="n">
-        <v>0.8818</v>
+        <v>0.8835</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>29.67</v>
+        <v>29.73</v>
       </c>
       <c r="C97" t="n">
-        <v>0.9064</v>
+        <v>0.9076</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>32.59</v>
+        <v>32.62</v>
       </c>
       <c r="C98" t="n">
-        <v>0.8764</v>
+        <v>0.877</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>29.16</v>
+        <v>29.38</v>
       </c>
       <c r="C99" t="n">
-        <v>0.9655</v>
+        <v>0.9668</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>25.91</v>
+        <v>25.88</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7601</v>
+        <v>0.7596000000000001</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>23.54</v>
+        <v>23.62</v>
       </c>
       <c r="C101" t="n">
-        <v>0.8892</v>
+        <v>0.8913</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27.25</v>
+        <v>27.28</v>
       </c>
       <c r="C102" t="n">
-        <v>0.9009</v>
+        <v>0.9018</v>
       </c>
     </row>
     <row r="103">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>22.86</v>
+        <v>23.31</v>
       </c>
       <c r="C103" t="n">
-        <v>0.8174</v>
+        <v>0.8293</v>
       </c>
     </row>
     <row r="104">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>36.52</v>
+        <v>36.76</v>
       </c>
       <c r="C104" t="n">
-        <v>0.9758</v>
+        <v>0.9762999999999999</v>
       </c>
     </row>
     <row r="105">
@@ -1791,10 +1791,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>28.79</v>
+        <v>28.82</v>
       </c>
       <c r="C105" t="n">
-        <v>0.9072</v>
+        <v>0.9078000000000001</v>
       </c>
     </row>
     <row r="106">
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>33.3</v>
+        <v>33.48</v>
       </c>
       <c r="C106" t="n">
-        <v>0.9752</v>
+        <v>0.9761</v>
       </c>
     </row>
     <row r="107">
@@ -1820,7 +1820,7 @@
         <v>29.56</v>
       </c>
       <c r="C107" t="n">
-        <v>0.886</v>
+        <v>0.8863</v>
       </c>
     </row>
     <row r="108">
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>36.73</v>
+        <v>36.52</v>
       </c>
       <c r="C108" t="n">
-        <v>0.9382</v>
+        <v>0.9381</v>
       </c>
     </row>
     <row r="109">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>31.56</v>
+        <v>31.6</v>
       </c>
       <c r="C109" t="n">
-        <v>0.8609</v>
+        <v>0.8617</v>
       </c>
     </row>
     <row r="110">
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>28.03</v>
+        <v>27.94</v>
       </c>
       <c r="C110" t="n">
-        <v>0.9036</v>
+        <v>0.902</v>
       </c>
     </row>
     <row r="111">
@@ -1869,10 +1869,10 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>30.49</v>
+        <v>30.55</v>
       </c>
       <c r="C111" t="n">
-        <v>0.9089</v>
+        <v>0.9096</v>
       </c>
     </row>
   </sheetData>
